--- a/Paket_2_Matematika_TKA_SD.xlsx
+++ b/Paket_2_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 2 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Panitia kegiatan bakti sosial menerima sumbangan beras sebanyak 15 karung. Masing-masing karung berisi 50 kg beras. Seluruh beras tersebut dikemas kembali ke dalam kantong plastik kecil berukuran 2,5 kg. Berapa banyak kantong plastik beras yang dihasilkan?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  250 kantong</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  300 kantong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  320 kantong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  350 kantong</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kapal selam mula-mula berada pada kedalaman 120 meter di bawah permukaan laut. Kapal selam tersebut kemudian naik sejauh 45 meter untuk menghindari terumbu karang. Beberapa saat kemudian, kapal kembali menyelam sedalam 20 meter. Posisi kedalaman kapal selam sekarang berada pada....</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  95 meter di bawah permukaan laut</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  85 meter di bawah permukaan laut</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  75 meter di bawah permukaan laut</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  65 meter di bawah permukaan laut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Pak Herman memiliki sebidang tanah seluas 1.200 m². Sebanyak 2/5 bagian dari tanah tersebut ditanami jagung, 25% ditanami cabai, dan sisanya dibuat kolam ikan lele. Berapakah luas tanah yang digunakan untuk kolam ikan lele?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  380 m²</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  420 m²</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  450 m²</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  480 m²</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,42 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Bu guru memiliki 36 pulpen biru, 54 buku tulis, dan 72 lembar kertas origami. Seluruh barang tersebut akan dibagikan kepada beberapa siswa berprestasi sebagai hadiah dengan jumlah tiap barang sama banyak tanpa sisa.
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Banyak siswa terbanyak yang menerima hadiah adalah 18 anak.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Setiap siswa menerima 2 pulpen biru.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Setiap siswa menerima 4 buku tulis.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Setiap siswa menerima 4 lembar kertas origami.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +638,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +652,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan bilangan-bilangan pecahan berikut:
+0,65  ;  5/8  ;  70%  ;  2/3
+Urutan bilangan pecahan tersebut mulai dari yang nilainya TERKECIL ke TERBESAR adalah....</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  5/8 ; 0,65 ; 2/3 ; 70%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  0,65 ; 5/8 ; 70% ; 2/3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  5/8 ; 2/3 ; 0,65 ; 70%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  2/3 ; 5/8 ; 0,65 ; 70%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +685,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Bibi memasak menggunakan minyak goreng. Di dapur tersedia 1 1/2 liter minyak. Bibi membeli lagi 2 botol minyak kemasan masing-masing berisi 0,75 liter. Hari ini Bibi menggunakan 2 1/4 liter minyak untuk menggoreng kerupuk. Tentukan kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +730,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +744,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Lampu mercusuar merah berkedip setiap 15 detik, lampu hijau setiap 20 detik, dan lampu kuning setiap 30 detik. Jika ketiga lampu berkedip bersamaan pada pukul 19.45.00, pada pukul berapakah ketiga lampu akan berkedip bersama-sama untuk kedua kalinya?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  19.45.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  19.46.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  19.46.30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  19.47.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +775,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +789,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Pekerjaan merenovasi pos ronda diperkirakan dapat diselesaikan oleh 6 orang tukang dalam waktu 12 hari. Jika pekerjaan tersebut ingin diselesaikan dalam waktu 8 hari, berapa banyak tukang yang dibutuhkan seluruhnya?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  8 orang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  9 orang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  10 orang</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  12 orang</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +820,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +834,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Bus Bintang berangkat dari terminal pada pukul 08.00 dengan kecepatan rata-rata 50 km/jam. Pada pukul 08.30, mobil Avanza menyusul melewati rute jalan yang sama dengan kecepatan rata-rata 75 km/jam. Pada pukul berapakah mobil Avanza berhasil menyusul bus Bintang?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  09.00 WIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  09.30 WIB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  10.00 WIB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  10.30 WIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +865,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +879,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Usia kakek saat ini adalah 7 dasawarsa lebih 3 tahun. Sedangkan usia paman adalah 4 windu lebih 2 tahun. Selisih usia kakek dan paman adalah....</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  37 tahun</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  39 tahun</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  41 tahun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  43 tahun</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +910,42 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah roda sepeda anak memiliki panjang jari-jari 21 cm. Roda tersebut berputar menggelinding sebanyak 100 kali putaran di lintasan lurus. (Gunakan π = 22/7).
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Keliling roda sepeda tersebut adalah 132 cm.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Panjang lintasan yang ditempuh roda adalah 132 meter.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Luas penampang roda tersebut adalah 1.386 cm².</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Diameter roda sepeda anak tersebut adalah 44 cm.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +956,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +970,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Pak Darmo memiliki sebidang tanah berbentuk trapesium sama kaki. Panjang sisi-sisi sejajarnya adalah 18 meter dan 30 meter, dengan jarak tegak (tinggi trapesium) 12 meter. Tanah tersebut akan dijual dengan harga Rp500.000 per meter persegi. Berapakah total uang yang diterima Pak Darmo dari penjualan tanah tersebut?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Rp144.000.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Rp156.000.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rp168.000.000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Rp180.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +1001,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1015,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah mobil tangki air menyalurkan air bersih ke bak penampungan warga sebanyak 4.200 liter dalam waktu 15 menit. Debit aliran air bersih tersebut adalah....</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  260 liter/menit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  280 liter/menit</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  300 liter/menit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  320 liter/menit</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1046,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1060,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah mainan anak tersusun dari balok berukuran panjang 12 cm, lebar 8 cm, tinggi 10 cm yang di atasnya tepat menempel sebuah kubus dengan panjang rusuk 8 cm. Berapakah volume gabungan seluruh mainan tersebut?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  1.472 cm³</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  1.512 cm³</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  1.624 cm³</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  1.728 cm³</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1091,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Sebuah tumpukan kubus satuan disusun sedemikian rupa. Tentukan nilai kebenaran dari prinsip visualisasi proyeksi bangun berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1136,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1150,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Diagram batang mendata berat badan (dalam kg) siswa kelas 6 SD:
+• Berat 32 kg: 6 siswa
+• Berat 34 kg: 10 siswa
+• Berat 36 kg: 8 siswa
+• Berat 38 kg: 4 siswa
+• Berat 40 kg: 2 siswa
+Berapakah persentase siswa yang memiliki berat badan lebih dari 35 kg terhadap seluruh siswa?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  40%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  45%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  46,7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  50%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1187,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1201,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Nilai rata-rata ulangan matematika dari 20 orang siswa adalah 76. Jika 5 orang siswa mengikuti ulangan susulan dengan nilai rata-rata 86 dan nilainya digabungkan, berapakah nilai rata-rata baru seluruh siswa tersebut?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  78</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  79</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  80</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1232,42 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Data jumlah gol yang dicetak seorang pemain bola dalam 10 pertandingan adalah: 1, 2, 0, 3, 2, 1, 2, 4, 1, 2.
+Manakah pernyataan analisis data berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Nilai modus dari data gol tersebut adalah 2.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Nilai median dari data gol tersebut adalah 2.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rata-rata gol per pertandingan adalah 1,8 gol.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Selisih gol terbanyak dan tersedikit (jangkauan) adalah 3 gol.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1278,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1292,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Tinggi badan seorang balita dicatat setiap 6 bulan: umur 12 bln (74 cm), 18 bln (80 cm), 24 bln (85 cm), 30 bln (91 cm), 36 bln (96 cm). Pada rentang usia berapakah balita tersebut mengalami pertambahan tinggi badan paling pesat?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Usia 12 - 18 bulan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Usia 18 - 24 bulan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Usia 24 - 30 bulan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Usia 30 - 36 bulan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1323,25 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 2] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Susunan korek api membentuk pola segitiga bertingkat:
+• Pola 1: membutuhkan 3 batang korek api
+• Pola 2: membutuhkan 5 batang korek api
+• Pola 3: membutuhkan 7 batang korek api
+Tentukan kebenaran dari pernyataan berikut mengenai pola tersebut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1372,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
